--- a/Eastern Regions Report.xlsx
+++ b/Eastern Regions Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Excel Beginner\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C90ADF8-7746-4200-BF2D-76E9CB71450D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47B7B6FF-8779-4A66-81C6-5395DFADBD19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -881,6 +881,7 @@
   </mergeCells>
   <phoneticPr fontId="0" type="halfwidthKatakana" alignment="noControl"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0">
     <oddHeader>&amp;A</oddHeader>
     <oddFooter>Page &amp;P</oddFooter>
